--- a/data/trans_orig/IQ09_A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Tiempo medio en años que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,94</t>
+          <t>0,53; 3,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,68</t>
+          <t>1,0; 3,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,8</t>
+          <t>0,59; 3,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -761,24 +761,24 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,31</t>
+          <t>0,9; 3,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,37</t>
+          <t>0,23; 2,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,01</t>
+          <t>1,19; 3,85</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 8,83</t>
+          <t>0,42; 8,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 7,68</t>
+          <t>0,64; 8,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,7</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -896,29 +896,29 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 9,4</t>
+          <t>1,72; 8,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,89</t>
+          <t>0,85; 5,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 7,92</t>
+          <t>0,26; 9,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,16</t>
+          <t>0,76; 4,17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,57</t>
+          <t>4,95; 9,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 12,04</t>
+          <t>1,93; 10,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,15</t>
+          <t>2,87; 8,29</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,0</t>
+          <t>0,0; 9,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 8,12</t>
+          <t>0,18; 8,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,17</t>
+          <t>1,0; 6,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,23</t>
+          <t>0,35; 4,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,88</t>
+          <t>1,51; 6,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 8,84</t>
+          <t>2,25; 8,95</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,7</t>
+          <t>0,92; 6,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,17 +1311,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 8,06</t>
+          <t>0,71; 7,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,68</t>
+          <t>1,09; 3,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,4</t>
+          <t>1,33; 6,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,14 +1331,14 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,78</t>
+          <t>0,63; 7,28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,53</t>
+          <t>0,28; 1,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,15</t>
+          <t>2,02; 6,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 10,64</t>
+          <t>2,44; 9,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,24 +1461,24 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,9; 12,5</t>
+          <t>3,0; 13,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,1</t>
+          <t>1,39; 4,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 10,64</t>
+          <t>2,44; 9,98</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,08</t>
+          <t>0,55; 2,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,55</t>
+          <t>0,23; 4,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,67</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 6,78</t>
+          <t>0,0; 6,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 11,64</t>
+          <t>1,05; 11,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,67</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,63</t>
+          <t>0,61; 3,94</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,71</t>
+          <t>0,95; 8,89</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,2</t>
+          <t>1,24; 4,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,78</t>
+          <t>0,29; 2,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,0</t>
+          <t>0,0; 4,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,95; 8,5</t>
+          <t>1,85; 8,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,27</t>
+          <t>2,07; 7,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,52</t>
+          <t>0,1; 1,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,29</t>
+          <t>0,22; 5,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,39</t>
+          <t>2,26; 6,44</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,62</t>
+          <t>0,29; 1,6</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,61</t>
+          <t>0,09; 2,83</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,65</t>
+          <t>1,74; 6,47</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,53</t>
+          <t>1,31; 4,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,17</t>
+          <t>1,35; 3,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,39</t>
+          <t>0,9; 3,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,64</t>
+          <t>1,91; 4,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,16</t>
+          <t>1,98; 4,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,2</t>
+          <t>1,69; 4,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,75</t>
+          <t>1,35; 3,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,91</t>
+          <t>2,88; 5,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,17</t>
+          <t>1,98; 4,18</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,22</t>
+          <t>1,73; 3,24</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,94</t>
+          <t>1,37; 2,92</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,91</t>
+          <t>2,72; 4,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Provincia-trans_orig.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,96</t>
+          <t>0,52; 3,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,95</t>
+          <t>0,48; 3,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,76</t>
+          <t>0,63; 3,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,15</t>
+          <t>0,94; 3,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,43</t>
+          <t>0,33; 2,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,85</t>
+          <t>1,04; 3,95</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 8,63</t>
+          <t>0,42; 8,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 8,22</t>
+          <t>0,78; 8,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,46</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,27 +891,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,8</t>
+          <t>0,75; 4,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 8,74</t>
+          <t>1,98; 9,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,36</t>
+          <t>0,8; 4,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 9,38</t>
+          <t>0,25; 8,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,17</t>
+          <t>0,76; 4,1</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,91</t>
+          <t>4,95; 9,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 10,75</t>
+          <t>1,54; 10,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,29</t>
+          <t>2,99; 8,13</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,47</t>
+          <t>0,0; 8,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,47</t>
+          <t>0,35; 4,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,68</t>
+          <t>1,33; 6,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 8,95</t>
+          <t>1,85; 8,72</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 6,81</t>
+          <t>1,0; 7,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,68</t>
+          <t>0,8; 3,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,41</t>
+          <t>1,35; 6,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 7,28</t>
+          <t>0,54; 7,35</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,52</t>
+          <t>0,37; 1,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,44; 9,98</t>
+          <t>2,36; 10,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 13,0</t>
+          <t>3,0; 12,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,03</t>
+          <t>1,38; 3,95</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,44; 9,98</t>
+          <t>2,36; 10,37</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,0</t>
+          <t>0,62; 2,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,14</t>
+          <t>0,07; 3,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,84</t>
+          <t>0,21; 6,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 11,91</t>
+          <t>0,6; 11,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,94</t>
+          <t>0,59; 3,71</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,89</t>
+          <t>0,9; 8,99</t>
         </is>
       </c>
     </row>
@@ -1711,22 +1711,22 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,46</t>
+          <t>1,85; 8,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,81</t>
+          <t>2,09; 7,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,44</t>
+          <t>0,1; 1,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1736,22 +1736,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,44</t>
+          <t>2,38; 6,08</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,6</t>
+          <t>0,31; 1,61</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,83</t>
+          <t>0,09; 2,55</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,47</t>
+          <t>1,86; 6,52</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,84</t>
+          <t>1,31; 4,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,23</t>
+          <t>1,29; 3,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,2</t>
+          <t>0,92; 3,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,54</t>
+          <t>2,1; 4,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,93</t>
+          <t>1,86; 4,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,15</t>
+          <t>1,63; 4,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,83</t>
+          <t>1,32; 3,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,83</t>
+          <t>2,75; 5,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,18</t>
+          <t>1,97; 4,22</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,24</t>
+          <t>1,66; 3,21</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,92</t>
+          <t>1,32; 3,0</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,82</t>
+          <t>2,79; 4,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Provincia-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,96</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,35</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,34</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,34</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,66</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,82</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>2,23</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,65</t>
         </is>
       </c>
     </row>
@@ -716,42 +716,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 11,0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,61; 3,8</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,8</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,52; 3,76</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,59; 3,94</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0,0; 3,55</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,48; 3,36</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,63; 3,72</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,8</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,71</t>
+          <t>0,43; 3,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,11</t>
+          <t>0,89; 3,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,35</t>
+          <t>0,33; 2,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,95</t>
+          <t>0,93; 4,25</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,09</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,21</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,01</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,56</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,2</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,79</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,09</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,01</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 8,89</t>
+          <t>1,0; 15,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 8,31</t>
+          <t>0,25; 3,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 14,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0,85; 5,05</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,42; 8,83</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,5; 7,68</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,0</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 15,0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,82</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,75; 4,61</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 9,38</t>
+          <t>1,78; 9,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,7</t>
+          <t>0,84; 4,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 8,32</t>
+          <t>0,25; 7,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,1</t>
+          <t>0,75; 4,29</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,68</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,12</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,72</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,07</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,36</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,32</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,12</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,54</t>
+          <t>3,36</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,45</t>
+          <t>5,43</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1,0; 13,72</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5,08; 9,8</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>0,36; 5,0</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>0,0; 5,0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>0,0; 11,0</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,78</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1,95; 12,04</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>0,0; 5,0</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 13,72</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>4,95; 9,54</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,78</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1,54; 10,89</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,0</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,13</t>
+          <t>2,5; 8,3</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,48</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7,71</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2,0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,89</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,31</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,34</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,48</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,49</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,17</t>
+          <t>6,03</t>
         </is>
       </c>
     </row>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,64</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1,01; 6,17</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2,0; 10,0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0,0; 5,0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,71</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,18; 8,55</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,64</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,17</t>
+          <t>0,0; 9,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 10,0</t>
+          <t>0,35; 8,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,31</t>
+          <t>0,35; 4,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,73</t>
+          <t>1,33; 6,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,72</t>
+          <t>1,83; 8,44</t>
         </is>
       </c>
     </row>
@@ -1208,62 +1208,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,16</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>1,0</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,7</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2,51</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2,88</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3,22</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2,51</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2,88</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>2,87</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0,95; 6,7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0,31; 8,0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>2,0; 4,0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 7,11</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1,14; 3,68</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1,34; 6,4</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,71; 7,82</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0,8; 3,68</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1,35; 6,16</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 7,35</t>
+          <t>0,43; 6,69</t>
         </is>
       </c>
     </row>
@@ -1348,44 +1348,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12,33</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3,62</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4,9</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3,0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0,89</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,33</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,62</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4,67</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>4,9</t>
         </is>
       </c>
     </row>
@@ -1421,39 +1421,39 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>11,0; 13,0</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2,0; 6,15</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2,47; 11,24</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 1,62</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0,27; 1,53</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>11,0; 13,0</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>2,02; 6,31</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2,36; 10,37</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 12,5</t>
+          <t>4,9; 12,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,95</t>
+          <t>1,33; 4,1</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,36; 10,37</t>
+          <t>2,47; 11,24</t>
         </is>
       </c>
     </row>
@@ -1488,49 +1488,49 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,75</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,35</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4,84</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,21</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>0,75</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,75</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4,65</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t>1,45</t>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>3,71</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0,12; 2,67</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0,21; 6,78</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0,53; 11,95</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 2,08</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,64; 2,08</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 3,86</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,69</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,21; 6,82</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,0</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 11,4</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,12; 2,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,71</t>
+          <t>0,65; 3,63</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,99</t>
+          <t>0,92; 10,17</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4,2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,77</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2,44</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>3,01</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>1,29</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4,61</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,2</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>5,07</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,69</t>
+          <t>3,98</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,19</t>
+          <t>1,9; 7,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,9</t>
+          <t>0,1; 1,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,13</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,52</t>
+          <t>0,29; 6,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,09; 7,48</t>
+          <t>1,24; 4,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,33</t>
+          <t>0,28; 2,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 5,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 5,43</t>
+          <t>2,26; 8,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,08</t>
+          <t>2,34; 6,39</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,61</t>
+          <t>0,25; 1,62</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,55</t>
+          <t>0,18; 2,61</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,52</t>
+          <t>2,05; 7,11</t>
         </is>
       </c>
     </row>
@@ -1768,42 +1768,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,67</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,29</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4,18</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2,56</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2,02</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3,1</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,12</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,67</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>3,83</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,51</t>
+          <t>1,98; 5,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,15</t>
+          <t>1,67; 4,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,22</t>
+          <t>1,36; 3,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,72</t>
+          <t>2,85; 6,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,79</t>
+          <t>1,3; 4,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,11</t>
+          <t>1,31; 3,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,8</t>
+          <t>1,0; 3,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,9</t>
+          <t>1,88; 5,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,22</t>
+          <t>1,91; 4,17</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,21</t>
+          <t>1,63; 3,22</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,0</t>
+          <t>1,29; 2,94</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,93</t>
+          <t>2,84; 5,34</t>
         </is>
       </c>
     </row>
